--- a/analysis_outputs/rekap_validasi_test_batch16_split_80_10_10_70_15_15.xlsx
+++ b/analysis_outputs/rekap_validasi_test_batch16_split_80_10_10_70_15_15.xlsx
@@ -8,15 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan_Best_Val" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validasi_80_10_10" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validasi_70_15_15" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Best_Per_Split" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perbandingan_Split" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validasi_80_10_10" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validasi_70_15_15" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validasi_60_20_20" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Best_Per_Split" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ringkasan_Best_Val'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validasi_80_10_10'!$A$1:$L$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Validasi_70_15_15'!$A$1:$L$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test_Best_Per_Split'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ringkasan_Best_Val'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Perbandingan_Split'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Validasi_80_10_10'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Validasi_70_15_15'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Validasi_60_20_20'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test_Best_Per_Split'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,17 +28,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,11 +58,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,12 +71,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
       <bottom style="thin">
         <color rgb="00D9E2F3"/>
       </bottom>
@@ -82,20 +88,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -474,166 +483,212 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
     <col width="41" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Split</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Variant</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Epoch_Setting</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Batch</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Best_Val_Epoch_by_mAP50</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>mAP50</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mAP50-95</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Run_Name</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>80_10_10</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12N</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.70309</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.72859</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.7156129066551185</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.7912400000000001</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Dipakai untuk tabel test split 80_10_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>70_15_15</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>YOLOV12L</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="E2" s="4" t="n">
+      <c r="D3" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.69114</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G3" s="3" t="n">
         <v>0.72506</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H3" s="3" t="n">
         <v>0.7076937839288236</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I3" s="3" t="n">
         <v>0.7754799999999999</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.41242</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Dipakai untuk tabel test split 70_15_15</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>80_10_10</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12N</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0.70309</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.72859</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0.7156129066551185</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>0.7912400000000001</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0.39298</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Dipakai untuk tabel test split 80_10_10</t>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>60_20_20</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12S</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.63373</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.7255200000000001</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.676525715799154</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.73873</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Dipakai untuk tabel test split 60_20_20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -644,491 +699,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="72" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Rank_mAP50</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Best_Per_Split</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Variant</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Epoch_Setting</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Batch</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Validation_Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Best_Val_Epoch_by_mAP50</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Recall</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>mAP50</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>mAP50-95</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Run_Name</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Validation_mAP50</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Validation_F1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Internal_Test_mAP50</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Internal_Test_F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Internal_Test_Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Catatan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>YOLOV12N</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>80_10_10</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12N E50 B16</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0.70309</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0.72859</v>
-      </c>
-      <c r="I2" s="8" t="n">
+      <c r="D2" s="3" t="n">
+        <v>0.7912400000000001</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0.7156129066551185</v>
       </c>
-      <c r="J2" s="8" t="n">
-        <v>0.7912400000000001</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0.39298</v>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+      <c r="F2" s="3" t="n">
+        <v>0.7551453513733671</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.6183219938269687</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Best model selected by validation mAP50; tested on internal test split.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12N</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.75363</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0.77791</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>0.7655775406453635</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0.76612</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>0.38591</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12N_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>70_15_15</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12L E100 B16</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.7754799999999999</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.7076937839288236</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.6015102187896298</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.6010491916316369</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Best model selected by validation mAP50; tested on internal test split.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.53122</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0.72522</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0.6132427627264334</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0.67049</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0.34721</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.60742</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0.69895</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0.6499785037929531</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0.71714</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0.34866</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12M</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.59862</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0.83127</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0.6960183614124164</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0.68404</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0.36172</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12M_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12M</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.61502</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0.75676</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0.6785673142923793</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0.70562</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0.34258</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12M_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12L</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.66318</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>0.75889</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0.7078142007074195</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>0.7051500000000001</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0.35565</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12L_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12L</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.58832</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0.87945</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0.7050123984002943</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0.74025</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0.33639</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12X</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.49788</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>0.70403</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0.5832757134893628</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0.64627</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0.30026</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12X_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12X</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.7516</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>0.81641</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>0.7826656156529613</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0.76098</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0.41474</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12X_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>60_20_20</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12S E100 B16</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.73873</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.676525715799154</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.6605311229283004</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.620274837959925</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Best model selected by validation mAP50; tested on internal test split.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1153,108 +897,112 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Rank_mAP50</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Best_Per_Split</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Variant</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Epoch_Setting</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Batch</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Best_Val_Epoch_by_mAP50</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mAP50</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mAP50-95</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Run_Name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>YOLOV12N</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.68606</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0.7614</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>0.7217692841252953</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>0.70919</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>0.41334</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+      <c r="E2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.70309</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.72859</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.7156129066551185</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.7912400000000001</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
@@ -1262,8 +1010,8 @@
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>YOLOV12N</t>
         </is>
@@ -1275,77 +1023,77 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.63706</v>
+        <v>0.75363</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.78195</v>
+        <v>0.77791</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.7021079019880057</v>
+        <v>0.7655775406453635</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.75974</v>
+        <v>0.76612</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0.3871</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12N_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.38591</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S</t>
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>16</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.68781</v>
+        <v>0.7516</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.74757</v>
+        <v>0.81641</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.7164459887973917</v>
+        <v>0.7826656156529613</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.72077</v>
+        <v>0.76098</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.40437</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.41474</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S</t>
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
@@ -1355,75 +1103,75 @@
         <v>16</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.7255</v>
+        <v>0.58832</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.70257</v>
+        <v>0.87945</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.7138509106696452</v>
+        <v>0.7050123984002943</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.7547199999999999</v>
+        <v>0.74025</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.42084</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.33639</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12M</t>
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>16</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.6687</v>
+        <v>0.60742</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.7430600000000001</v>
+        <v>0.69895</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.7039216609055363</v>
+        <v>0.6499785037929531</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.73103</v>
+        <v>0.71714</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.40441</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12M_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.34866</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>YOLOV12M</t>
         </is>
@@ -1435,35 +1183,35 @@
         <v>16</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.6904</v>
+        <v>0.61502</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.74763</v>
+        <v>0.75676</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.7178761945161088</v>
+        <v>0.6785673142923793</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.75229</v>
+        <v>0.70562</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.40043</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12M_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.34258</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M_192_E100_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>YOLOV12L</t>
         </is>
@@ -1475,81 +1223,77 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.7255200000000001</v>
+        <v>0.66318</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.72222</v>
+        <v>0.75889</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.7238662389655601</v>
+        <v>0.7078142007074195</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.74673</v>
+        <v>0.7051500000000001</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.41396</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12L_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.35565</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>YOLOV12L</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>88</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>0.69114</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0.72506</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>0.7076937839288236</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>0.7754799999999999</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>0.41242</v>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.59862</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.83127</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.6960183614124164</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.68404</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12X</t>
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -1562,63 +1306,63 @@
         <v>30</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.71334</v>
+        <v>0.53122</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.72056</v>
+        <v>0.72522</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.7169318228607294</v>
+        <v>0.6132427627264334</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.73532</v>
+        <v>0.67049</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.38748</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12X_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.34721</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>YOLOV12X</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>16</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.71535</v>
+        <v>0.49788</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.69987</v>
+        <v>0.70403</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.7075253381099758</v>
+        <v>0.5832757134893628</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.73414</v>
+        <v>0.64627</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.39028</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>YOLOV12X_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        <v>0.30026</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1378,997 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_mAP50</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Per_Split</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Epoch_Setting</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Val_Epoch_by_mAP50</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mAP50</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mAP50-95</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Run_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12L</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.69114</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.72506</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.7076937839288236</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.7754799999999999</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.63706</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.78195</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.7021079019880057</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0.75974</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.7255</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.70257</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.7138509106696452</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.7547199999999999</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.42084</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.6904</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.74763</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.7178761945161088</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.75229</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.7255200000000001</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.72222</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0.7238662389655601</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.74673</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.71334</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.72056</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.7169318228607294</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0.73532</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.71535</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.69987</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.7075253381099758</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.73414</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.6687</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.7430600000000001</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.7039216609055363</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.73103</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.68781</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.74757</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.7164459887973917</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.72077</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.68606</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.7614</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.7217692841252953</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.70919</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rank_mAP50</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Per_Split</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Epoch_Setting</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Val_Epoch_by_mAP50</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mAP50</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mAP50-95</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Run_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12S</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.63373</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.7255200000000001</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.676525715799154</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.73873</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.64149</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.68671</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.6633302181900317</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0.72379</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.6348</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.71758</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.6736564929975303</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.71716</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.59127</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.6743</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.6300613336283256</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.71509</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E50_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.6184500000000001</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.76107</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0.6823877022442589</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0.71345</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.6357</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.71511</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.6730708641481778</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0.70838</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12N_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.7750899999999999</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.6427150128771573</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.70552</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12L_192_E50_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.61544</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.70695</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.6580287328246583</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0.70017</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12X_192_E50_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.54286</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.70351</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.6128315646236671</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.67623</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.64944</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.61538</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.6319514036779937</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.66601</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.34147</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>YOLOV12M_192_E50_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1646,203 +2380,261 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="13" max="13"/>
+    <col width="72" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Split</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Selected_From_Validation</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Validation_Best_Epoch_by_mAP50</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Validation_mAP50</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Test_Status</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>mAP50</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mAP50-95</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Test_Metrics_CSV</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Model_Path</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Data_Path</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Run_Name</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>80_10_10</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>YOLOV12N E50 B16</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.7912400000000001</v>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>FOUND</t>
         </is>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="3" t="n">
         <v>0.5974608434168509</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="3" t="n">
         <v>0.6406926406926406</v>
       </c>
-      <c r="H2" s="8" t="n">
+      <c r="H2" s="3" t="n">
         <v>0.6183219938269687</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="3" t="n">
         <v>0.7551453513733671</v>
       </c>
-      <c r="J2" s="8" t="n">
+      <c r="J2" s="3" t="n">
         <v>0.4258796257028965</v>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\runs\detect_test\batch_size_16\YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop_test\test_metrics.csv</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\runs\detect\batch_size_16\YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop\weights\best.pt</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\yolo_new_gen\dataset_yolo_det_192_3class_vv_vh_rgb_scene_80_10_10_seed7\data.yaml</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>YOLOV12N_192_E50_B16_3class_VV_VH_RGB_scene_80_10_10_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>70_15_15</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>YOLOV12L E100 B16</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.7754799999999999</v>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>FOUND</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.6186999469890712</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="3" t="n">
         <v>0.5843776106934001</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="3" t="n">
         <v>0.6010491916316369</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="3" t="n">
         <v>0.6015102187896298</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.2969997549945489</v>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\runs\detect_test\batch_size_16\YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop_best_test\test_metrics.csv</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\runs\detect\batch_size_16\YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop\weights\best.pt</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\yolo_new_gen\dataset_yolo_det_192_3class_vv_vh_rgb_scene_70_15_15_seed7\data.yaml</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>YOLOV12L_192_E100_B16_3class_VV_VH_RGB_scene_70_15_15_seed7_adamw_lr0005_nomosaic_noearlystop</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>60_20_20</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12S E100 B16</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.73873</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FOUND</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.6102697066270487</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.6306134977304541</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.620274837959925</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.6605311229283004</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.3527450949461724</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\runs\detect_test\batch_size_16\YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop_test\test_metrics.csv</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\runs\detect\batch_size_16\YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop\weights\best.pt</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>E:\FILEALE\01YATUHANFIXBGTYOLOGFW\yolo_new_gen\dataset_yolo_det_192_3class_vv_vh_rgb_scene_60_20_20_seed7\data.yaml</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>YOLOV12S_192_E100_B16_3class_VV_VH_RGB_scene_60_20_20_seed7_adamw_lr0005_nomosaic_noearlystop</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>